--- a/docs/data/jp/xlsx/6629.xlsx
+++ b/docs/data/jp/xlsx/6629.xlsx
@@ -2073,7 +2073,7 @@
     <row r="7">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t>Imaging And ITReportable Segments</t>
+          <t>영상·IT 사업</t>
         </is>
       </c>
       <c r="B7" s="10" t="n"/>
@@ -2355,7 +2355,7 @@
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>Robotics Reportable Segments</t>
+          <t>로보틱스 사업</t>
         </is>
       </c>
       <c r="B10" s="10" t="n"/>
@@ -11097,7 +11097,7 @@
     <row r="159">
       <c r="A159" s="18" t="inlineStr">
         <is>
-          <t>부문 · 외부 고객 매출</t>
+          <t>영상·IT 사업 · 외부 고객 매출</t>
         </is>
       </c>
       <c r="C159" s="20" t="n">
@@ -11205,7 +11205,7 @@
     <row r="161">
       <c r="A161" s="18" t="inlineStr">
         <is>
-          <t>부문 · 외부 고객 매출</t>
+          <t>로보틱스 사업 · 외부 고객 매출</t>
         </is>
       </c>
       <c r="C161" s="20" t="n">
@@ -11581,7 +11581,7 @@
     <row r="168">
       <c r="A168" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 간 내부매출·대체</t>
+          <t>영상·IT 사업 · 부문 간 내부매출·대체</t>
         </is>
       </c>
       <c r="C168" s="20" t="n">
@@ -11633,7 +11633,7 @@
     <row r="169">
       <c r="A169" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 간 내부매출·대체</t>
+          <t>로보틱스 사업 · 부문 간 내부매출·대체</t>
         </is>
       </c>
       <c r="C169" s="20" t="n">
@@ -11841,7 +11841,7 @@
     <row r="173">
       <c r="A173" s="18" t="inlineStr">
         <is>
-          <t>부문 · 계</t>
+          <t>영상·IT 사업 · 계</t>
         </is>
       </c>
       <c r="C173" s="20" t="n">
@@ -11949,7 +11949,7 @@
     <row r="175">
       <c r="A175" s="18" t="inlineStr">
         <is>
-          <t>부문 · 계</t>
+          <t>로보틱스 사업 · 계</t>
         </is>
       </c>
       <c r="C175" s="20" t="n">
@@ -12325,7 +12325,7 @@
     <row r="182">
       <c r="A182" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 이익(손실)</t>
+          <t>영상·IT 사업 · 부문 이익(손실)</t>
         </is>
       </c>
       <c r="C182" s="20" t="n">
@@ -12505,7 +12505,7 @@
     <row r="185">
       <c r="A185" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 이익(손실)</t>
+          <t>로보틱스 사업 · 부문 이익(손실)</t>
         </is>
       </c>
       <c r="C185" s="20" t="n">
@@ -14319,7 +14319,7 @@
     <row r="226">
       <c r="A226" s="18" t="inlineStr">
         <is>
-          <t>Loss On Valuation Of Software Ope CF</t>
+          <t>소프트웨어 평가손</t>
         </is>
       </c>
       <c r="D226" s="20" t="n">
